--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Records Manager" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Records Manager" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Records Manager'!$A$4:$I$12</definedName>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Records Manager" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Records Manager" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Records Manager'!$A$4:$I$12</definedName>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Records Manager" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Records Manager" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Records Manager'!$A$4:$I$12</definedName>
@@ -832,7 +832,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Current discovery-setting decision record, transition note, and access-request workflow evidence; Model-policy record for Anthropic family and any enabled provider-retention model variants; Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy plus recent Cost management and Cowork usage reports; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved tool-server inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local tool output, third-party inference telemetry)</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
